--- a/相似系所研究表現評比.xlsx
+++ b/相似系所研究表現評比.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\系所雷同比較Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F0D754-02FA-4583-8E6F-CC474A333F8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20EC74B-DE35-4C8D-B4F4-D9DA73BB9074}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="Export Details" sheetId="2" r:id="rId2"/>
     <sheet name="Percentile Thresholds" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="58">
   <si>
     <t>﻿Entity</t>
   </si>
@@ -190,13 +190,19 @@
   </si>
   <si>
     <t>Researchers</t>
+  </si>
+  <si>
+    <t>平均總和</t>
+  </si>
+  <si>
+    <t>每師平均</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -210,6 +216,21 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -238,13 +259,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -559,14 +582,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="10" width="0" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -612,8 +635,29 @@
       <c r="O1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="4">
+        <v>2021</v>
+      </c>
+      <c r="R1" s="4">
+        <v>2022</v>
+      </c>
+      <c r="S1" s="4">
+        <v>2023</v>
+      </c>
+      <c r="T1" s="4">
+        <v>2024</v>
+      </c>
+      <c r="U1" s="4">
+        <v>2025</v>
+      </c>
+      <c r="V1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -659,8 +703,36 @@
       <c r="O2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>K2/K12</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="R2">
+        <f>L2/L12</f>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="S2">
+        <f>M2/M12</f>
+        <v>0.5</v>
+      </c>
+      <c r="T2">
+        <f>N2/N12</f>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="U2">
+        <f>O2/O12</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V2">
+        <f>SUM(Q2:U2)</f>
+        <v>2.9813519813519815</v>
+      </c>
+      <c r="W2" s="5">
+        <f>V2/5</f>
+        <v>0.59627039627039635</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -706,8 +778,36 @@
       <c r="O3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f>K3/K13</f>
+        <v>1.1538461538461537</v>
+      </c>
+      <c r="R3">
+        <f>L3/L13</f>
+        <v>1.3636363636363635</v>
+      </c>
+      <c r="S3">
+        <f>M3/M13</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T9" si="0">N3/N13</f>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U9" si="1">O3/O13</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V9" si="2">SUM(Q3:U3)</f>
+        <v>4.8187645687645686</v>
+      </c>
+      <c r="W3" s="5">
+        <f t="shared" ref="W3:W9" si="3">V3/5</f>
+        <v>0.96375291375291372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -753,8 +853,36 @@
       <c r="O4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f>K4/K14</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R9" si="4">L4/L14</f>
+        <v>0.2</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S3:S9" si="5">M4/M14</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="1"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="2"/>
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="W4" s="5">
+        <f t="shared" si="3"/>
+        <v>9.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -800,8 +928,36 @@
       <c r="O5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f>K5/K15</f>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="5"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="2"/>
+        <v>1.9636363636363638</v>
+      </c>
+      <c r="W5" s="5">
+        <f t="shared" si="3"/>
+        <v>0.39272727272727276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -847,8 +1003,36 @@
       <c r="O6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f>K6/K16</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="4"/>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="5"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="2"/>
+        <v>2.4341491841491845</v>
+      </c>
+      <c r="W6" s="5">
+        <f t="shared" si="3"/>
+        <v>0.48682983682983688</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -894,8 +1078,36 @@
       <c r="O7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f>K7/K17</f>
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
+        <v>1.2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="5"/>
+        <v>0.875</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="1"/>
+        <v>0.5625</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="2"/>
+        <v>3.9316176470588236</v>
+      </c>
+      <c r="W7" s="5">
+        <f t="shared" si="3"/>
+        <v>0.78632352941176475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -941,8 +1153,36 @@
       <c r="O8">
         <v>122</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" ref="Q4:Q9" si="6">K8/K18</f>
+        <v>3.2692307692307692</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="4"/>
+        <v>3.16</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="5"/>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>2.6206896551724137</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="1"/>
+        <v>4.0666666666666664</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="2"/>
+        <v>15.688015662498422</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" si="3"/>
+        <v>3.1376031324996845</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -988,8 +1228,36 @@
       <c r="O9">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>1.4166666666666667</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="5"/>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="1"/>
+        <v>1.3636363636363635</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="2"/>
+        <v>6.4726107226107228</v>
+      </c>
+      <c r="W9" s="5">
+        <f t="shared" si="3"/>
+        <v>1.2945221445221446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1021,7 +1289,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1056,7 +1324,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1091,7 +1359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1126,7 +1394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1161,7 +1429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>

--- a/相似系所研究表現評比.xlsx
+++ b/相似系所研究表現評比.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20EC74B-DE35-4C8D-B4F4-D9DA73BB9074}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F5A35B-FD7A-4E29-8C96-DB72BB7B11C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
         <v>0.2</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S3:S9" si="5">M4/M14</f>
+        <f t="shared" ref="S4:S9" si="5">M4/M14</f>
         <v>0</v>
       </c>
       <c r="T4">
@@ -1154,15 +1154,15 @@
         <v>122</v>
       </c>
       <c r="Q8">
-        <f t="shared" ref="Q4:Q9" si="6">K8/K18</f>
+        <f>K8/K18</f>
         <v>3.2692307692307692</v>
       </c>
       <c r="R8">
-        <f t="shared" si="4"/>
+        <f>L8/L18</f>
         <v>3.16</v>
       </c>
       <c r="S8">
-        <f t="shared" si="5"/>
+        <f>M8/M18</f>
         <v>2.5714285714285716</v>
       </c>
       <c r="T8">
@@ -1174,11 +1174,11 @@
         <v>4.0666666666666664</v>
       </c>
       <c r="V8">
-        <f t="shared" si="2"/>
+        <f>SUM(Q8:U8)</f>
         <v>15.688015662498422</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" si="3"/>
+        <f>V8/5</f>
         <v>3.1376031324996845</v>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="Q8:Q9" si="6">K9/K19</f>
         <v>1.4166666666666667</v>
       </c>
       <c r="R9">

--- a/相似系所研究表現評比.xlsx
+++ b/相似系所研究表現評比.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDF57A2-7AD4-458D-8DF4-191258E21FB5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E50B3B9B-E085-4600-96FB-8121E27774FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="Export Details" sheetId="2" r:id="rId2"/>
     <sheet name="Percentile Thresholds" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="61">
   <si>
     <t>﻿Entity</t>
   </si>
@@ -48,19 +48,142 @@
     <t/>
   </si>
   <si>
+    <t>企業管理系*</t>
+  </si>
+  <si>
+    <t>NKUST</t>
+  </si>
+  <si>
+    <t>Scholarly Output</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>All publication types</t>
+  </si>
+  <si>
+    <t>國際企業系*</t>
+  </si>
+  <si>
+    <t>財務管理系*</t>
+  </si>
+  <si>
+    <t>財政稅務系*</t>
+  </si>
+  <si>
+    <t>金融系*</t>
+  </si>
+  <si>
+    <t>電子工程系[建工|燕巢校區]*</t>
+  </si>
+  <si>
+    <t>電子工程系[第一]*</t>
+  </si>
+  <si>
+    <t>International Collaboration (%)</t>
+  </si>
+  <si>
+    <t>Academic-Corporate Collaboration (%)</t>
+  </si>
+  <si>
+    <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
+  </si>
+  <si>
+    <t>in top 10% by CiteScore Percentile</t>
+  </si>
+  <si>
+    <t>Output in Top 10% Citation Percentiles (%)</t>
+  </si>
+  <si>
+    <t>included</t>
+  </si>
+  <si>
+    <t>in top 10% of the world</t>
+  </si>
+  <si>
+    <t>Subject Area Main Category Count</t>
+  </si>
+  <si>
+    <t>Field-Weighted Citation Impact</t>
+  </si>
+  <si>
+    <t>* Only publications affiliated with National Kaohsiung University of Science and Technology included</t>
+  </si>
+  <si>
+    <t>© 2026 Elsevier B.V. All rights reserved. SciVal, RELX Group and the RE symbol are trade marks of RELX Intellectual Properties SA, used under license.</t>
+  </si>
+  <si>
+    <t>﻿Data set</t>
+  </si>
+  <si>
+    <t>Multiple Metrics</t>
+  </si>
+  <si>
+    <t>Entities</t>
+  </si>
+  <si>
+    <t>企業管理系*, 國際企業系*, 財務管理系*, 財政稅務系*, 金融系*, 電子工程系[建工|燕巢校區]*, 電子工程系[第一]*</t>
+  </si>
+  <si>
+    <t>Year range</t>
+  </si>
+  <si>
+    <t>2018 to 2025</t>
+  </si>
+  <si>
+    <t>Subject classification</t>
+  </si>
+  <si>
+    <t>ASJC</t>
+  </si>
+  <si>
+    <t>Filtered by</t>
+  </si>
+  <si>
+    <t>All subject areas</t>
+  </si>
+  <si>
+    <t>Data source</t>
+  </si>
+  <si>
+    <t>Scopus</t>
+  </si>
+  <si>
+    <t>Date last updated</t>
+  </si>
+  <si>
+    <t>30 August 2026</t>
+  </si>
+  <si>
+    <t>Date exported</t>
+  </si>
+  <si>
+    <t>8 September 2026</t>
+  </si>
+  <si>
+    <t>﻿</t>
+  </si>
+  <si>
+    <t>Citation thresholds for Outputs in Top Citation Percentiles (all publication types)</t>
+  </si>
+  <si>
+    <t>Top 1%</t>
+  </si>
+  <si>
+    <t>Top 5%</t>
+  </si>
+  <si>
+    <t>Top 10%</t>
+  </si>
+  <si>
+    <t>Top 25%</t>
+  </si>
+  <si>
     <t>企業管理系</t>
   </si>
   <si>
-    <t>NKUST</t>
-  </si>
-  <si>
-    <t>Scholarly Output</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>All publication types</t>
+    <t>Researchers</t>
   </si>
   <si>
     <t>國際企業系</t>
@@ -82,115 +205,13 @@
   </si>
   <si>
     <t>電子工程系[第一]</t>
-  </si>
-  <si>
-    <t>International Collaboration (%)</t>
-  </si>
-  <si>
-    <t>Academic-Corporate Collaboration (%)</t>
-  </si>
-  <si>
-    <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
-  </si>
-  <si>
-    <t>in top 10% by CiteScore Percentile</t>
-  </si>
-  <si>
-    <t>Output in Top 10% Citation Percentiles (%)</t>
-  </si>
-  <si>
-    <t>included</t>
-  </si>
-  <si>
-    <t>in top 10% of the world</t>
-  </si>
-  <si>
-    <t>Subject Area Main Category Count</t>
-  </si>
-  <si>
-    <t>Field-Weighted Citation Impact</t>
-  </si>
-  <si>
-    <t>© 2026 Elsevier B.V. All rights reserved. SciVal, RELX Group and the RE symbol are trade marks of RELX Intellectual Properties SA, used under license.</t>
-  </si>
-  <si>
-    <t>﻿Data set</t>
-  </si>
-  <si>
-    <t>Multiple Metrics</t>
-  </si>
-  <si>
-    <t>Entities</t>
-  </si>
-  <si>
-    <t>企業管理系, 國際企業系, 會計資訊系, 財務管理系, 財政稅務系, 金融系, 電子工程系[建工|燕巢校區], 電子工程系[第一]</t>
-  </si>
-  <si>
-    <t>Year range</t>
-  </si>
-  <si>
-    <t>2021 to 2025</t>
-  </si>
-  <si>
-    <t>Subject classification</t>
-  </si>
-  <si>
-    <t>ASJC</t>
-  </si>
-  <si>
-    <t>Filtered by</t>
-  </si>
-  <si>
-    <t>All subject areas</t>
-  </si>
-  <si>
-    <t>Data source</t>
-  </si>
-  <si>
-    <t>Scopus</t>
-  </si>
-  <si>
-    <t>Date last updated</t>
-  </si>
-  <si>
-    <t>29 July 2026</t>
-  </si>
-  <si>
-    <t>Date exported</t>
-  </si>
-  <si>
-    <t>11 August 2026</t>
-  </si>
-  <si>
-    <t>﻿</t>
-  </si>
-  <si>
-    <t>Citation thresholds for Outputs in Top Citation Percentiles (all publication types)</t>
-  </si>
-  <si>
-    <t>Top 1%</t>
-  </si>
-  <si>
-    <t>Top 5%</t>
-  </si>
-  <si>
-    <t>Top 10%</t>
-  </si>
-  <si>
-    <t>Top 25%</t>
-  </si>
-  <si>
-    <t>Researchers</t>
-  </si>
-  <si>
-    <t>每系專任教師數取自改質躍升 (產學_每師平均產學收入.xlsx)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -206,14 +227,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -247,12 +260,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -567,10 +579,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -634,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>7</v>
@@ -672,16 +685,16 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -710,22 +723,22 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -748,19 +761,19 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -786,22 +799,22 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -824,22 +837,22 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>497</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -862,88 +875,76 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>434</v>
+        <v>105</v>
       </c>
       <c r="H8">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>78</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
-      <c r="J9">
-        <v>12</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-      <c r="L9">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="1">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1">
+        <v>12</v>
+      </c>
+      <c r="L10" s="1">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I11" s="1">
+        <v>11</v>
+      </c>
+      <c r="J11" s="1">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1">
         <v>13</v>
-      </c>
-      <c r="J11" s="1">
-        <v>14</v>
-      </c>
-      <c r="K11" s="1">
-        <v>12</v>
       </c>
       <c r="L11" s="1">
         <v>13</v>
@@ -951,195 +952,214 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L12" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I13" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I14" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J14" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L14" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="1">
+        <v>15</v>
+      </c>
+      <c r="I15" s="1">
+        <v>15</v>
+      </c>
+      <c r="J15" s="1">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="1">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
-        <v>13</v>
-      </c>
-      <c r="J15" s="1">
-        <v>12</v>
-      </c>
       <c r="K15" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L15" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I16" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J16" s="1">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K16" s="1">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L16" s="1">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I17" s="1">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J17" s="1">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K17" s="1">
-        <v>29</v>
-      </c>
-      <c r="L17" s="1">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="L17" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="1">
-        <v>12</v>
-      </c>
-      <c r="I18" s="1">
-        <v>12</v>
-      </c>
-      <c r="J18" s="1">
-        <v>13</v>
-      </c>
-      <c r="K18" s="1">
-        <v>13</v>
-      </c>
-      <c r="L18" s="2">
-        <v>11</v>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>13.6</v>
+      </c>
+      <c r="H19">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>21.4</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1151,33 +1171,33 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>13.5</v>
+        <v>36.6</v>
       </c>
       <c r="H20">
         <v>16.7</v>
       </c>
       <c r="I20">
-        <v>12.5</v>
+        <v>28.6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K20">
-        <v>21.4</v>
+        <v>45.5</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1189,33 +1209,33 @@
         <v>11</v>
       </c>
       <c r="G21">
-        <v>39</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H21">
-        <v>33.299999999999997</v>
+        <v>25</v>
       </c>
       <c r="I21">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K21">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="L21">
-        <v>71.400000000000006</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1227,33 +1247,33 @@
         <v>11</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>56.1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="J22">
+        <v>40</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1265,33 +1285,33 @@
         <v>11</v>
       </c>
       <c r="G23">
-        <v>31.6</v>
+        <v>38.1</v>
       </c>
       <c r="H23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="J23">
-        <v>25</v>
+        <v>88.9</v>
       </c>
       <c r="K23">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="L23">
-        <v>25</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1303,33 +1323,33 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="H24">
-        <v>60</v>
+        <v>27.3</v>
       </c>
       <c r="I24">
-        <v>40</v>
+        <v>43.1</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K24">
-        <v>66.7</v>
+        <v>22.7</v>
       </c>
       <c r="L24">
-        <v>50</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1341,65 +1361,32 @@
         <v>11</v>
       </c>
       <c r="G25">
-        <v>50.8</v>
+        <v>5.7</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>7.1</v>
       </c>
       <c r="I25">
-        <v>61.1</v>
+        <v>4.3</v>
       </c>
       <c r="J25">
-        <v>78.599999999999994</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K25">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>33.299999999999997</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="H26">
-        <v>24.7</v>
-      </c>
-      <c r="I26">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="J26">
-        <v>29.2</v>
-      </c>
-      <c r="K26">
-        <v>23.7</v>
-      </c>
-      <c r="L26">
-        <v>52.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -1417,38 +1404,71 @@
         <v>11</v>
       </c>
       <c r="G27">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>8.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>13.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1.2</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1480,13 +1500,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -1518,13 +1538,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1544,8 +1564,8 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" t="s">
-        <v>11</v>
+      <c r="J31">
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -1556,13 +1576,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -1574,33 +1594,33 @@
         <v>11</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1612,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1627,50 +1647,17 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -1685,30 +1672,30 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G35">
-        <v>2.5</v>
+        <v>31</v>
       </c>
       <c r="H35">
-        <v>2.4</v>
+        <v>40</v>
       </c>
       <c r="I35">
-        <v>1.3</v>
+        <v>60</v>
       </c>
       <c r="J35">
-        <v>6.9</v>
+        <v>28.6</v>
       </c>
       <c r="K35">
-        <v>1.3</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="L35">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -1723,659 +1710,692 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G36">
-        <v>1.3</v>
+        <v>22.1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="L36">
-        <v>6.7</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37">
+        <v>15.4</v>
+      </c>
+      <c r="H37">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>25</v>
+      </c>
+      <c r="K37">
+        <v>20</v>
+      </c>
+      <c r="L37">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
         <v>22</v>
       </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>23</v>
-      </c>
       <c r="G38">
-        <v>35.1</v>
+        <v>12.5</v>
       </c>
       <c r="H38">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>50</v>
       </c>
-      <c r="J38">
-        <v>28.6</v>
-      </c>
-      <c r="K38">
-        <v>35.700000000000003</v>
-      </c>
       <c r="L38">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
         <v>22</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>23</v>
-      </c>
       <c r="G39">
-        <v>23.6</v>
+        <v>21.6</v>
       </c>
       <c r="H39">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="L39">
-        <v>33.299999999999997</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
         <v>22</v>
       </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>23</v>
-      </c>
       <c r="G40">
-        <v>33.299999999999997</v>
+        <v>20.9</v>
       </c>
       <c r="H40">
-        <v>100</v>
+        <v>21.7</v>
       </c>
       <c r="I40">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="J40" t="s">
-        <v>11</v>
+        <v>15.7</v>
+      </c>
+      <c r="J40">
+        <v>25.5</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
         <v>22</v>
       </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" t="s">
-        <v>23</v>
-      </c>
       <c r="G41">
-        <v>22.2</v>
+        <v>13</v>
       </c>
       <c r="H41">
-        <v>33.299999999999997</v>
+        <v>9.1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K41">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="L41">
-        <v>25</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42">
-        <v>17.2</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>50</v>
-      </c>
-      <c r="L42">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G43">
-        <v>29.4</v>
+        <v>22.7</v>
       </c>
       <c r="H43">
-        <v>33.299999999999997</v>
+        <v>40</v>
       </c>
       <c r="I43">
-        <v>15.4</v>
+        <v>60</v>
       </c>
       <c r="J43">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="K43">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="L43">
-        <v>55.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G44">
-        <v>20.6</v>
+        <v>8.5</v>
       </c>
       <c r="H44">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>18</v>
+        <v>14.3</v>
       </c>
       <c r="J44">
-        <v>22.6</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>21.9</v>
+        <v>9.1</v>
       </c>
       <c r="L44">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G45">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>18.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>2.4</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>20</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
       </c>
       <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
         <v>24</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
         <v>25</v>
       </c>
-      <c r="E47" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" t="s">
-        <v>26</v>
-      </c>
       <c r="G47">
-        <v>29.7</v>
+        <v>14.3</v>
       </c>
       <c r="H47">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>42.9</v>
+        <v>22.2</v>
       </c>
       <c r="K47">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
       </c>
       <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
         <v>24</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
         <v>25</v>
       </c>
-      <c r="E48" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" t="s">
-        <v>26</v>
-      </c>
       <c r="G48">
-        <v>6.8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="I48">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="J48">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="K48">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
       </c>
       <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
         <v>24</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
         <v>25</v>
       </c>
-      <c r="E49" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" t="s">
-        <v>26</v>
-      </c>
       <c r="G49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49" t="s">
-        <v>11</v>
+      <c r="J49">
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G51">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
         <v>17</v>
       </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52">
-        <v>24.6</v>
-      </c>
       <c r="H52">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="I52">
-        <v>11.1</v>
+        <v>9</v>
       </c>
       <c r="J52">
-        <v>35.700000000000003</v>
+        <v>11</v>
       </c>
       <c r="K52">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L52">
-        <v>11.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G53">
-        <v>8.3000000000000007</v>
+        <v>13</v>
       </c>
       <c r="H53">
-        <v>14.1</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>5.0999999999999996</v>
+        <v>7</v>
       </c>
       <c r="J53">
-        <v>9.6999999999999993</v>
+        <v>7</v>
       </c>
       <c r="K53">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>7.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="H54">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L54">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>12</v>
+      </c>
+      <c r="H55">
+        <v>6</v>
+      </c>
+      <c r="I55">
+        <v>6</v>
+      </c>
+      <c r="J55">
         <v>7</v>
+      </c>
+      <c r="K55">
+        <v>4</v>
+      </c>
+      <c r="L55">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2387,33 +2407,33 @@
         <v>11</v>
       </c>
       <c r="G56">
+        <v>24</v>
+      </c>
+      <c r="H56">
+        <v>19</v>
+      </c>
+      <c r="I56">
         <v>14</v>
       </c>
-      <c r="H56">
-        <v>7</v>
-      </c>
-      <c r="I56">
-        <v>6</v>
-      </c>
       <c r="J56">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K56">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2428,62 +2448,29 @@
         <v>14</v>
       </c>
       <c r="H57">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I57">
         <v>10</v>
       </c>
       <c r="J57">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K57">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L57">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58">
-        <v>6</v>
-      </c>
-      <c r="H58">
-        <v>2</v>
-      </c>
-      <c r="I58">
-        <v>4</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>3</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -2492,7 +2479,7 @@
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
@@ -2501,27 +2488,27 @@
         <v>11</v>
       </c>
       <c r="G59">
-        <v>13</v>
+        <v>1.22</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>2.77</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>1.44</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
@@ -2530,7 +2517,7 @@
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
@@ -2539,27 +2526,27 @@
         <v>11</v>
       </c>
       <c r="G60">
-        <v>10</v>
+        <v>0.73</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>0.42</v>
       </c>
       <c r="I60">
-        <v>8</v>
+        <v>0.74</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>0.67</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -2568,7 +2555,7 @@
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
         <v>12</v>
@@ -2577,27 +2564,27 @@
         <v>11</v>
       </c>
       <c r="G61">
-        <v>15</v>
+        <v>0.33</v>
       </c>
       <c r="H61">
-        <v>12</v>
+        <v>0.18</v>
       </c>
       <c r="I61">
-        <v>12</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>0.21</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>0.61</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -2606,7 +2593,7 @@
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -2615,27 +2602,27 @@
         <v>11</v>
       </c>
       <c r="G62">
-        <v>25</v>
+        <v>0.47</v>
       </c>
       <c r="H62">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="I62">
-        <v>14</v>
+        <v>0.64</v>
       </c>
       <c r="J62">
-        <v>16</v>
+        <v>0.6</v>
       </c>
       <c r="K62">
-        <v>20</v>
+        <v>0.27</v>
       </c>
       <c r="L62">
-        <v>19</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -2644,7 +2631,7 @@
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
         <v>12</v>
@@ -2653,41 +2640,74 @@
         <v>11</v>
       </c>
       <c r="G63">
-        <v>16</v>
+        <v>0.88</v>
       </c>
       <c r="H63">
-        <v>12</v>
+        <v>0.9</v>
       </c>
       <c r="I63">
-        <v>10</v>
+        <v>0.27</v>
       </c>
       <c r="J63">
-        <v>9</v>
+        <v>1.56</v>
       </c>
       <c r="K63">
-        <v>10</v>
+        <v>0.98</v>
       </c>
       <c r="L63">
-        <v>7</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64">
+        <v>0.73</v>
+      </c>
+      <c r="H64">
+        <v>0.94</v>
+      </c>
+      <c r="I64">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J64">
+        <v>0.78</v>
+      </c>
+      <c r="K64">
+        <v>0.66</v>
+      </c>
+      <c r="L64">
+        <v>0.63</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
         <v>12</v>
@@ -2696,307 +2716,51 @@
         <v>11</v>
       </c>
       <c r="G65">
-        <v>1.35</v>
+        <v>0.45</v>
       </c>
       <c r="H65">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="I65">
-        <v>2.13</v>
+        <v>0.46</v>
       </c>
       <c r="J65">
-        <v>1.45</v>
+        <v>0.46</v>
       </c>
       <c r="K65">
-        <v>1.1499999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="L65">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66">
-        <v>0.65</v>
-      </c>
-      <c r="H66">
-        <v>0.4</v>
-      </c>
-      <c r="I66">
-        <v>0.71</v>
-      </c>
-      <c r="J66">
-        <v>1.05</v>
-      </c>
-      <c r="K66">
-        <v>0.68</v>
-      </c>
-      <c r="L66">
-        <v>0.37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67">
-        <v>0.66</v>
-      </c>
-      <c r="H67">
-        <v>0.59</v>
-      </c>
-      <c r="I67">
-        <v>0.59</v>
-      </c>
-      <c r="J67" t="s">
-        <v>11</v>
-      </c>
-      <c r="K67">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>28</v>
-      </c>
-      <c r="D68" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68">
-        <v>0.3</v>
-      </c>
-      <c r="H68">
-        <v>0.18</v>
-      </c>
-      <c r="I68">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J68">
-        <v>0.22</v>
-      </c>
-      <c r="K68">
-        <v>0.59</v>
-      </c>
-      <c r="L68">
-        <v>0.16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>16</v>
-      </c>
-      <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" t="s">
         <v>28</v>
-      </c>
-      <c r="D69" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69">
-        <v>0.49</v>
-      </c>
-      <c r="H69">
-        <v>0.3</v>
-      </c>
-      <c r="I69">
-        <v>0.64</v>
-      </c>
-      <c r="J69">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="K69">
-        <v>0.27</v>
-      </c>
-      <c r="L69">
-        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70">
-        <v>1.48</v>
-      </c>
-      <c r="H70">
-        <v>2.19</v>
-      </c>
-      <c r="I70">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="J70">
-        <v>1.65</v>
-      </c>
-      <c r="K70">
-        <v>0.83</v>
-      </c>
-      <c r="L70">
-        <v>1.1599999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>18</v>
-      </c>
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71">
-        <v>0.74</v>
-      </c>
-      <c r="H71">
-        <v>0.96</v>
-      </c>
-      <c r="I71">
-        <v>0.53</v>
-      </c>
-      <c r="J71">
-        <v>0.94</v>
-      </c>
-      <c r="K71">
-        <v>0.65</v>
-      </c>
-      <c r="L71">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>19</v>
-      </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72">
-        <v>0.42</v>
-      </c>
-      <c r="H72">
-        <v>0.53</v>
-      </c>
-      <c r="I72">
-        <v>0.44</v>
-      </c>
-      <c r="J72">
-        <v>0.45</v>
-      </c>
-      <c r="K72">
-        <v>0.18</v>
-      </c>
-      <c r="L72">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3007,10 +2771,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -3018,7 +2782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3026,7 +2790,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3034,7 +2798,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -3042,7 +2806,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -3050,31 +2814,28 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -3082,17 +2843,17 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -3105,20 +2866,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3126,22 +2887,31 @@
         <v>7</v>
       </c>
       <c r="C3">
+        <v>2018</v>
+      </c>
+      <c r="D3">
+        <v>2019</v>
+      </c>
+      <c r="E3">
+        <v>2020</v>
+      </c>
+      <c r="F3">
         <v>2021</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>2022</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>2023</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>2024</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -3149,25 +2919,34 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="D4">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="E4">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="F4">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="G4">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4">
+        <v>93</v>
+      </c>
+      <c r="I4">
+        <v>64</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -3175,25 +2954,34 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>38</v>
+      </c>
+      <c r="I5">
+        <v>27</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -3201,25 +2989,34 @@
         <v>7</v>
       </c>
       <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+      <c r="F6">
         <v>38</v>
       </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
       <c r="G6">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -3227,21 +3024,30 @@
         <v>7</v>
       </c>
       <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="G7">
         <v>14</v>
       </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>7</v>
       </c>
     </row>

--- a/相似系所研究表現評比.xlsx
+++ b/相似系所研究表現評比.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E50B3B9B-E085-4600-96FB-8121E27774FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5A20D3-B10D-40A3-BF22-831D89661CD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/相似系所研究表現評比.xlsx
+++ b/相似系所研究表現評比.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5A20D3-B10D-40A3-BF22-831D89661CD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3330F4EB-4608-44A7-A23F-D34960123282}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="53">
   <si>
     <t>﻿Entity</t>
   </si>
@@ -48,7 +48,7 @@
     <t/>
   </si>
   <si>
-    <t>企業管理系*</t>
+    <t>企業管理系</t>
   </si>
   <si>
     <t>NKUST</t>
@@ -63,22 +63,25 @@
     <t>All publication types</t>
   </si>
   <si>
-    <t>國際企業系*</t>
-  </si>
-  <si>
-    <t>財務管理系*</t>
-  </si>
-  <si>
-    <t>財政稅務系*</t>
-  </si>
-  <si>
-    <t>金融系*</t>
-  </si>
-  <si>
-    <t>電子工程系[建工|燕巢校區]*</t>
-  </si>
-  <si>
-    <t>電子工程系[第一]*</t>
+    <t>國際企業系</t>
+  </si>
+  <si>
+    <t>會計資訊系</t>
+  </si>
+  <si>
+    <t>財務管理系</t>
+  </si>
+  <si>
+    <t>財政稅務系</t>
+  </si>
+  <si>
+    <t>金融系</t>
+  </si>
+  <si>
+    <t>電子工程系[建工|燕巢校區]</t>
+  </si>
+  <si>
+    <t>電子工程系[第一]</t>
   </si>
   <si>
     <t>International Collaboration (%)</t>
@@ -108,9 +111,6 @@
     <t>Field-Weighted Citation Impact</t>
   </si>
   <si>
-    <t>* Only publications affiliated with National Kaohsiung University of Science and Technology included</t>
-  </si>
-  <si>
     <t>© 2026 Elsevier B.V. All rights reserved. SciVal, RELX Group and the RE symbol are trade marks of RELX Intellectual Properties SA, used under license.</t>
   </si>
   <si>
@@ -123,13 +123,13 @@
     <t>Entities</t>
   </si>
   <si>
-    <t>企業管理系*, 國際企業系*, 財務管理系*, 財政稅務系*, 金融系*, 電子工程系[建工|燕巢校區]*, 電子工程系[第一]*</t>
+    <t>企業管理系, 國際企業系, 會計資訊系, 財務管理系, 財政稅務系, 金融系, 電子工程系[建工|燕巢校區], 電子工程系[第一]</t>
   </si>
   <si>
     <t>Year range</t>
   </si>
   <si>
-    <t>2018 to 2025</t>
+    <t>2021 to 2025</t>
   </si>
   <si>
     <t>Subject classification</t>
@@ -159,7 +159,7 @@
     <t>Date exported</t>
   </si>
   <si>
-    <t>8 September 2026</t>
+    <t>9 September 2026</t>
   </si>
   <si>
     <t>﻿</t>
@@ -180,38 +180,14 @@
     <t>Top 25%</t>
   </si>
   <si>
-    <t>企業管理系</t>
-  </si>
-  <si>
     <t>Researchers</t>
-  </si>
-  <si>
-    <t>國際企業系</t>
-  </si>
-  <si>
-    <t>會計資訊系</t>
-  </si>
-  <si>
-    <t>財務管理系</t>
-  </si>
-  <si>
-    <t>財政稅務系</t>
-  </si>
-  <si>
-    <t>金融系</t>
-  </si>
-  <si>
-    <t>電子工程系[建工|燕巢校區]</t>
-  </si>
-  <si>
-    <t>電子工程系[第一]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -225,13 +201,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -260,11 +229,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -579,12 +547,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -647,13 +611,13 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>7</v>
@@ -685,16 +649,16 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -723,22 +687,22 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>2</v>
       </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
       <c r="L4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -761,19 +725,19 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <v>5</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -799,22 +763,22 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
+      <c r="L6">
         <v>4</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -837,22 +801,22 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>497</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>113</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -875,291 +839,385 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>78</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="1">
-        <v>11</v>
-      </c>
-      <c r="I10" s="1">
-        <v>13</v>
-      </c>
-      <c r="J10" s="1">
-        <v>14</v>
-      </c>
-      <c r="K10" s="1">
-        <v>12</v>
-      </c>
-      <c r="L10" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="1">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
-        <v>11</v>
-      </c>
-      <c r="J11" s="1">
-        <v>12</v>
-      </c>
-      <c r="K11" s="1">
-        <v>13</v>
-      </c>
-      <c r="L11" s="1">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>13.5</v>
+      </c>
+      <c r="H11">
+        <v>16.7</v>
+      </c>
+      <c r="I11">
+        <v>12.5</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>21.4</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="1">
-        <v>16</v>
-      </c>
-      <c r="I12" s="1">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1">
-        <v>14</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="1">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>39</v>
+      </c>
+      <c r="H12">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I12">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="J12">
+        <v>27.3</v>
+      </c>
+      <c r="K12">
+        <v>45.5</v>
+      </c>
+      <c r="L12">
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="1">
-        <v>11</v>
-      </c>
-      <c r="I13" s="1">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1">
-        <v>9</v>
-      </c>
-      <c r="K13" s="1">
-        <v>9</v>
-      </c>
-      <c r="L13" s="1">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="1">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
-        <v>13</v>
-      </c>
-      <c r="J14" s="1">
-        <v>12</v>
-      </c>
-      <c r="K14" s="1">
-        <v>12</v>
-      </c>
-      <c r="L14" s="1">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>31.6</v>
+      </c>
+      <c r="H14">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>25</v>
+      </c>
+      <c r="K14">
+        <v>60</v>
+      </c>
+      <c r="L14">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="1">
-        <v>15</v>
-      </c>
-      <c r="I15" s="1">
-        <v>15</v>
-      </c>
-      <c r="J15" s="1">
-        <v>16</v>
-      </c>
-      <c r="K15" s="1">
-        <v>17</v>
-      </c>
-      <c r="L15" s="1">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>60</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15">
+        <v>66.7</v>
+      </c>
+      <c r="L15">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="1">
-        <v>26</v>
-      </c>
-      <c r="I16" s="1">
-        <v>25</v>
-      </c>
-      <c r="J16" s="1">
-        <v>28</v>
-      </c>
-      <c r="K16" s="1">
-        <v>29</v>
-      </c>
-      <c r="L16" s="1">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>50.8</v>
+      </c>
+      <c r="H16">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>61.1</v>
+      </c>
+      <c r="J16">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="K16">
+        <v>60</v>
+      </c>
+      <c r="L16">
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="1">
-        <v>12</v>
-      </c>
-      <c r="I17" s="1">
-        <v>12</v>
-      </c>
-      <c r="J17" s="1">
-        <v>13</v>
-      </c>
-      <c r="K17" s="1">
-        <v>13</v>
-      </c>
-      <c r="L17" s="2">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="H17">
+        <v>24.7</v>
+      </c>
+      <c r="I17">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="J17">
+        <v>29.2</v>
+      </c>
+      <c r="K17">
+        <v>23.7</v>
+      </c>
+      <c r="L17">
+        <v>52.5</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>6.4</v>
+      </c>
+      <c r="H18">
+        <v>5.9</v>
+      </c>
+      <c r="I18">
+        <v>4.2</v>
+      </c>
+      <c r="J18">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>13.3</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>13.6</v>
-      </c>
-      <c r="H19">
-        <v>20</v>
-      </c>
-      <c r="I19">
-        <v>20</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>21.4</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1171,33 +1229,33 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>36.6</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>71.400000000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1209,33 +1267,33 @@
         <v>11</v>
       </c>
       <c r="G21">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1247,33 +1305,33 @@
         <v>11</v>
       </c>
       <c r="G22">
-        <v>56.1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>40</v>
-      </c>
-      <c r="J22">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>11</v>
       </c>
       <c r="K22">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1285,33 +1343,33 @@
         <v>11</v>
       </c>
       <c r="G23">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>88.9</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1323,33 +1381,33 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>35.200000000000003</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>43.1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>53.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1361,38 +1419,71 @@
         <v>11</v>
       </c>
       <c r="G25">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>8.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>2.5</v>
+      </c>
+      <c r="H26">
+        <v>2.4</v>
+      </c>
+      <c r="I26">
+        <v>1.3</v>
+      </c>
+      <c r="J26">
+        <v>6.9</v>
+      </c>
+      <c r="K26">
+        <v>1.3</v>
+      </c>
+      <c r="L26">
+        <v>1.6</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -1404,7 +1495,7 @@
         <v>11</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1419,56 +1510,23 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>1.2</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1477,22 +1535,22 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>35.1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1500,51 +1558,51 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>23.6</v>
+      </c>
+      <c r="H30">
+        <v>7.1</v>
+      </c>
+      <c r="I30">
+        <v>28.6</v>
+      </c>
+      <c r="J30">
         <v>20</v>
       </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
       <c r="K30">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1553,19 +1611,19 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
+        <v>33.299999999999997</v>
+      </c>
+      <c r="J31" t="s">
+        <v>11</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -1576,51 +1634,51 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32">
+        <v>22.2</v>
+      </c>
+      <c r="H32">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>25</v>
+      </c>
+      <c r="K32">
         <v>20</v>
       </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32">
-        <v>2.8</v>
-      </c>
-      <c r="H32">
-        <v>3</v>
-      </c>
-      <c r="I32">
-        <v>1.5</v>
-      </c>
-      <c r="J32">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
       <c r="L32">
-        <v>1.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1629,10 +1687,10 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>17.2</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1644,26 +1702,59 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L33">
-        <v>7.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34">
+        <v>29.4</v>
+      </c>
+      <c r="H34">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I34">
+        <v>15.4</v>
+      </c>
+      <c r="J34">
+        <v>25</v>
+      </c>
+      <c r="K34">
+        <v>20</v>
+      </c>
+      <c r="L34">
+        <v>55.6</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -1672,36 +1763,36 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G35">
-        <v>31</v>
+        <v>20.6</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="I35">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J35">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="K35">
-        <v>35.700000000000003</v>
+        <v>21.9</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -1710,322 +1801,322 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G36">
-        <v>22.1</v>
+        <v>13.3</v>
       </c>
       <c r="H36">
-        <v>8.3000000000000007</v>
+        <v>21.4</v>
       </c>
       <c r="I36">
-        <v>23.1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="K36">
-        <v>36.4</v>
+        <v>11.1</v>
       </c>
       <c r="L36">
-        <v>33.299999999999997</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37">
-        <v>15.4</v>
-      </c>
-      <c r="H37">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>25</v>
-      </c>
-      <c r="K37">
-        <v>20</v>
-      </c>
-      <c r="L37">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>12.5</v>
+        <v>29.7</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K38">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="L38">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G39">
-        <v>21.6</v>
+        <v>6.8</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="K39">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="L39">
-        <v>55.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G40">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>15.7</v>
-      </c>
-      <c r="J40">
-        <v>25.5</v>
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>11</v>
       </c>
       <c r="K40">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>17.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>18.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42">
+        <v>3.3</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E43" t="s">
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G43">
-        <v>22.7</v>
+        <v>24.6</v>
       </c>
       <c r="H43">
         <v>40</v>
       </c>
       <c r="I43">
-        <v>60</v>
+        <v>11.1</v>
       </c>
       <c r="J43">
-        <v>42.9</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="K43">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G44">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="I44">
-        <v>14.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J44">
-        <v>10</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K44">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2034,216 +2125,216 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46">
-        <v>2.4</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>20</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>22.2</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L47">
-        <v>11.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>8.1999999999999993</v>
+        <v>14</v>
       </c>
       <c r="H48">
-        <v>12.1</v>
+        <v>9</v>
       </c>
       <c r="I48">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="J48">
+        <v>11</v>
+      </c>
+      <c r="K48">
+        <v>9</v>
+      </c>
+      <c r="L48">
         <v>10</v>
-      </c>
-      <c r="K48">
-        <v>6.1</v>
-      </c>
-      <c r="L48">
-        <v>7.1</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G49">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="H49">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <v>11.1</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>7.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>13</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
         <v>7</v>
+      </c>
+      <c r="J50">
+        <v>7</v>
+      </c>
+      <c r="K50">
+        <v>5</v>
+      </c>
+      <c r="L50">
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>10</v>
+      </c>
+      <c r="H51">
+        <v>6</v>
+      </c>
+      <c r="I51">
         <v>8</v>
       </c>
-      <c r="B51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51">
-        <v>15</v>
-      </c>
-      <c r="H51">
-        <v>7</v>
-      </c>
-      <c r="I51">
+      <c r="J51">
         <v>6</v>
       </c>
-      <c r="J51">
-        <v>4</v>
-      </c>
       <c r="K51">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2255,71 +2346,71 @@
         <v>11</v>
       </c>
       <c r="G52">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H52">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I52">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J52">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K52">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L52">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>25</v>
+      </c>
+      <c r="H53">
+        <v>19</v>
+      </c>
+      <c r="I53">
         <v>14</v>
       </c>
-      <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53">
-        <v>13</v>
-      </c>
-      <c r="H53">
-        <v>2</v>
-      </c>
-      <c r="I53">
-        <v>7</v>
-      </c>
       <c r="J53">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2331,74 +2422,41 @@
         <v>11</v>
       </c>
       <c r="G54">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55">
-        <v>12</v>
-      </c>
-      <c r="H55">
-        <v>6</v>
-      </c>
-      <c r="I55">
-        <v>6</v>
-      </c>
-      <c r="J55">
         <v>7</v>
-      </c>
-      <c r="K55">
-        <v>4</v>
-      </c>
-      <c r="L55">
-        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
         <v>12</v>
@@ -2407,36 +2465,36 @@
         <v>11</v>
       </c>
       <c r="G56">
-        <v>24</v>
+        <v>1.35</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>1.02</v>
       </c>
       <c r="I56">
-        <v>14</v>
+        <v>2.15</v>
       </c>
       <c r="J56">
-        <v>15</v>
+        <v>1.44</v>
       </c>
       <c r="K56">
-        <v>18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="L56">
-        <v>19</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
         <v>12</v>
@@ -2445,41 +2503,74 @@
         <v>11</v>
       </c>
       <c r="G57">
-        <v>14</v>
+        <v>0.64</v>
       </c>
       <c r="H57">
-        <v>11</v>
+        <v>0.4</v>
       </c>
       <c r="I57">
-        <v>10</v>
+        <v>0.72</v>
       </c>
       <c r="J57">
-        <v>9</v>
+        <v>1.02</v>
       </c>
       <c r="K57">
-        <v>10</v>
+        <v>0.67</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <v>0.64</v>
+      </c>
+      <c r="H58">
+        <v>0.59</v>
+      </c>
+      <c r="I58">
+        <v>0.59</v>
+      </c>
+      <c r="J58" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58">
+        <v>1.07</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
@@ -2488,36 +2579,36 @@
         <v>11</v>
       </c>
       <c r="G59">
-        <v>1.22</v>
+        <v>0.33</v>
       </c>
       <c r="H59">
-        <v>1.18</v>
+        <v>0.18</v>
       </c>
       <c r="I59">
-        <v>2.77</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J59">
-        <v>1.44</v>
+        <v>0.21</v>
       </c>
       <c r="K59">
-        <v>1.1599999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="L59">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
@@ -2526,36 +2617,36 @@
         <v>11</v>
       </c>
       <c r="G60">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="H60">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="I60">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="J60">
-        <v>1.1299999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="K60">
-        <v>0.67</v>
+        <v>0.27</v>
       </c>
       <c r="L60">
-        <v>0.33</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
         <v>12</v>
@@ -2564,36 +2655,36 @@
         <v>11</v>
       </c>
       <c r="G61">
-        <v>0.33</v>
+        <v>1.48</v>
       </c>
       <c r="H61">
-        <v>0.18</v>
+        <v>2.19</v>
       </c>
       <c r="I61">
-        <v>0.28999999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J61">
-        <v>0.21</v>
+        <v>1.67</v>
       </c>
       <c r="K61">
-        <v>0.61</v>
+        <v>0.81</v>
       </c>
       <c r="L61">
-        <v>0.26</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -2602,36 +2693,36 @@
         <v>11</v>
       </c>
       <c r="G62">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.96</v>
       </c>
       <c r="I62">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="J62">
-        <v>0.6</v>
+        <v>0.94</v>
       </c>
       <c r="K62">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="L62">
-        <v>0.56000000000000005</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
         <v>12</v>
@@ -2640,127 +2731,249 @@
         <v>11</v>
       </c>
       <c r="G63">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="H63">
-        <v>0.9</v>
+        <v>0.53</v>
       </c>
       <c r="I63">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="J63">
-        <v>1.56</v>
+        <v>0.46</v>
       </c>
       <c r="K63">
-        <v>0.98</v>
+        <v>0.18</v>
       </c>
       <c r="L63">
-        <v>1.1299999999999999</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64">
-        <v>0.73</v>
-      </c>
-      <c r="H64">
-        <v>0.94</v>
-      </c>
-      <c r="I64">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J64">
-        <v>0.78</v>
-      </c>
-      <c r="K64">
-        <v>0.66</v>
-      </c>
-      <c r="L64">
-        <v>0.63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65">
-        <v>0.45</v>
-      </c>
-      <c r="H65">
-        <v>0.59</v>
-      </c>
-      <c r="I65">
-        <v>0.46</v>
-      </c>
-      <c r="J65">
-        <v>0.46</v>
-      </c>
-      <c r="K65">
-        <v>0.16</v>
-      </c>
-      <c r="L65">
-        <v>0.39</v>
+        <v>52</v>
+      </c>
+      <c r="H65" s="1">
+        <v>11</v>
+      </c>
+      <c r="I65" s="1">
+        <v>13</v>
+      </c>
+      <c r="J65" s="1">
+        <v>14</v>
+      </c>
+      <c r="K65" s="1">
+        <v>12</v>
+      </c>
+      <c r="L65" s="1">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="1">
+        <v>13</v>
+      </c>
+      <c r="I66" s="1">
+        <v>11</v>
+      </c>
+      <c r="J66" s="1">
+        <v>12</v>
+      </c>
+      <c r="K66" s="1">
+        <v>13</v>
+      </c>
+      <c r="L66" s="1">
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>52</v>
+      </c>
+      <c r="H67" s="1">
+        <v>16</v>
+      </c>
+      <c r="I67" s="1">
+        <v>15</v>
+      </c>
+      <c r="J67" s="1">
+        <v>14</v>
+      </c>
+      <c r="K67" s="1">
+        <v>15</v>
+      </c>
+      <c r="L67" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>52</v>
+      </c>
+      <c r="H68" s="1">
+        <v>11</v>
+      </c>
+      <c r="I68" s="1">
+        <v>10</v>
+      </c>
+      <c r="J68" s="1">
+        <v>9</v>
+      </c>
+      <c r="K68" s="1">
+        <v>9</v>
+      </c>
+      <c r="L68" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="1">
+        <v>13</v>
+      </c>
+      <c r="I69" s="1">
+        <v>13</v>
+      </c>
+      <c r="J69" s="1">
+        <v>12</v>
+      </c>
+      <c r="K69" s="1">
+        <v>12</v>
+      </c>
+      <c r="L69" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70" s="1">
+        <v>15</v>
+      </c>
+      <c r="I70" s="1">
+        <v>15</v>
+      </c>
+      <c r="J70" s="1">
+        <v>16</v>
+      </c>
+      <c r="K70" s="1">
+        <v>17</v>
+      </c>
+      <c r="L70" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="1">
+        <v>26</v>
+      </c>
+      <c r="I71" s="1">
+        <v>25</v>
+      </c>
+      <c r="J71" s="1">
+        <v>28</v>
+      </c>
+      <c r="K71" s="1">
+        <v>29</v>
+      </c>
+      <c r="L71" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="1">
+        <v>12</v>
+      </c>
+      <c r="I72" s="1">
+        <v>12</v>
+      </c>
+      <c r="J72" s="1">
+        <v>13</v>
+      </c>
+      <c r="K72" s="1">
+        <v>13</v>
+      </c>
+      <c r="L72" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2831,7 +3044,7 @@
       <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2860,26 +3073,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2887,31 +3099,22 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D3">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E3">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="F3">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G3">
-        <v>2022</v>
-      </c>
-      <c r="H3">
-        <v>2023</v>
-      </c>
-      <c r="I3">
-        <v>2024</v>
-      </c>
-      <c r="J3">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -2919,34 +3122,25 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="D4">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="F4">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="G4">
-        <v>120</v>
-      </c>
-      <c r="H4">
-        <v>93</v>
-      </c>
-      <c r="I4">
-        <v>64</v>
-      </c>
-      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
+      <c r="H4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -2954,34 +3148,25 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D5">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E5">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>49</v>
-      </c>
-      <c r="H5">
-        <v>38</v>
-      </c>
-      <c r="I5">
-        <v>27</v>
-      </c>
-      <c r="J5">
         <v>13</v>
       </c>
-      <c r="K5" t="s">
+      <c r="H5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -2989,34 +3174,25 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>31</v>
-      </c>
-      <c r="H6">
-        <v>24</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
         <v>8</v>
       </c>
-      <c r="K6" t="s">
+      <c r="H6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -3024,30 +3200,21 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>14</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7" t="s">
+      <c r="H7" t="s">
         <v>7</v>
       </c>
     </row>
